--- a/novos_leads.xlsx
+++ b/novos_leads.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -46,8 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z1"/>
+  <dimension ref="A1:V4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -514,37 +518,271 @@
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>first_name</t>
+          <t>Concordo em Receber Comunicações</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>last_name</t>
+          <t>Telefone</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>mobilephone</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>Concordo em Receber Comunicações</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>Telefone</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
           <t>telefone</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>escolha_seu_curso</t>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>l:1043090545311776</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ag:120259623620270537</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Transf. Intern. | Banner | Mulheres na Escada</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>as:120259602865020537</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Lookalike Inscritos</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>c:120259602864830537</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Pareto | Lorena | Lead ads | Medicina | 26.2 | Transferência Internacional</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>f:2296658154476727</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>LORENA - Medicina - Transf.Internacional 07/2026</t>
+        </is>
+      </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>ig</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Geruza Gomes</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>drageruzagomes@gmail.com</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>5579991249336</v>
+      </c>
+      <c r="Q2" t="b">
+        <v>1</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>l:1035481842227861</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ag:120259623620270537</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Transf. Intern. | Banner | Mulheres na Escada</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>as:120259602865020537</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Lookalike Inscritos</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>c:120259602864830537</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Pareto | Lorena | Lead ads | Medicina | 26.2 | Transferência Internacional</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>f:2296658154476727</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>LORENA - Medicina - Transf.Internacional 07/2026</t>
+        </is>
+      </c>
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>ig</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Profa Adriana Vilano Dinamarco</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>adinamarco.lyra@gmail.com</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>551332211338</v>
+      </c>
+      <c r="Q3" t="b">
+        <v>1</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>l:27370923692590002</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ag:Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>as:Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>c:Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>f:1840466290646742</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>LORENA - Regulares | TO 07/2026</t>
+        </is>
+      </c>
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>ig</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Flavia Bortoleto</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>flaviabortoleto4@gmail.com</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="b">
+        <v>1</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>p:+5512997562435</t>
         </is>
       </c>
     </row>

--- a/novos_leads.xlsx
+++ b/novos_leads.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V4"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -535,50 +535,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>l:1043090545311776</t>
+          <t>l:4635658106654998</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ag:120259623620270537</t>
+          <t>ag:120249230124020610</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Transf. Intern. | Banner | Mulheres na Escada</t>
+          <t>Terapia Ocupacional | Banner | Duas Mulheres</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>as:120259602865020537</t>
+          <t>as:120249229519180610</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lookalike Inscritos</t>
+          <t>Lookalike Matriculados | LoginCRM</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>c:120259602864830537</t>
+          <t>c:120249229519170610</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pareto | Lorena | Lead ads | Medicina | 26.2 | Transferência Internacional</t>
+          <t>Pareto | Itabirito | Leads Ads | Regulares | 26.2 - TO</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>f:2296658154476727</t>
+          <t>f:27688517784091361</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>LORENA - Medicina - Transf.Internacional 07/2026</t>
+          <t>Itabirito - Regulares | TO 07/2026</t>
         </is>
       </c>
       <c r="K2" t="b">
@@ -590,36 +590,36 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Geruza Gomes</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
-          <t>drageruzagomes@gmail.com</t>
+          <t>mariaclaudialimaferreira9@gmail.com</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>5579991249336</v>
-      </c>
-      <c r="Q2" t="b">
+        <v>5512991243122</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Maria Claudia</t>
+        </is>
+      </c>
+      <c r="T2" t="b">
         <v>1</v>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>l:1035481842227861</t>
+          <t>l:2609020686183293</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
@@ -627,42 +627,42 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ag:120259623620270537</t>
+          <t>ag:120249230124020610</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Transf. Intern. | Banner | Mulheres na Escada</t>
+          <t>Terapia Ocupacional | Banner | Duas Mulheres</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>as:120259602865020537</t>
+          <t>as:120249229519180610</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lookalike Inscritos</t>
+          <t>Lookalike Matriculados | LoginCRM</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>c:120259602864830537</t>
+          <t>c:120249229519170610</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pareto | Lorena | Lead ads | Medicina | 26.2 | Transferência Internacional</t>
+          <t>Pareto | Itabirito | Leads Ads | Regulares | 26.2 - TO</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>f:2296658154476727</t>
+          <t>f:27688517784091361</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>LORENA - Medicina - Transf.Internacional 07/2026</t>
+          <t>Itabirito - Regulares | TO 07/2026</t>
         </is>
       </c>
       <c r="K3" t="b">
@@ -674,40 +674,40 @@
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Profa Adriana Vilano Dinamarco</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>adinamarco.lyra@gmail.com</t>
+          <t>tcristinaprincesa@gmail.com</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>551332211338</v>
-      </c>
-      <c r="Q3" t="b">
+        <v>5535998243081</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Teresa Cristina De Macedo</t>
+        </is>
+      </c>
+      <c r="T3" t="b">
         <v>1</v>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>l:27370923692590002</t>
+          <t>l:1547628913721293</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -741,12 +741,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>f:1840466290646742</t>
+          <t>f:1149489480748786</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>LORENA - Regulares | TO 07/2026</t>
+          <t>LORENA - Cursos Livres | 07/2026</t>
         </is>
       </c>
       <c r="K4" t="b">
@@ -757,15 +757,19 @@
           <t>ig</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Técnicas emersão orofacial</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Flavia Bortoleto</t>
+          <t>𝑫𝒂𝒏𝒊𝒆𝒍 𝑯𝒆𝒓𝒏𝒂𝒏𝒅𝒆𝒔</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>flaviabortoleto4@gmail.com</t>
+          <t>nielhernandes204@gmail.com</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
@@ -779,12 +783,694 @@
       </c>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>p:+5512997562435</t>
-        </is>
-      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>5512991538409</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>l:988809387537755</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ag:Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>as:Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>c:Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>f:1149489480748786</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>LORENA - Cursos Livres | 07/2026</t>
+        </is>
+      </c>
+      <c r="K5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>ig</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>imersão em HOF</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Leticia Dias</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>diasleticia531@gmail.com</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="b">
+        <v>1</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>5512996449688</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>l:2651632011939417</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ag:Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>as:Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>c:Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>f:1149489480748786</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>LORENA - Cursos Livres | 07/2026</t>
+        </is>
+      </c>
+      <c r="K6" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>ig</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Chics Modas | Atacado de Roupas</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>clararmarques@hotmail.com</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="b">
+        <v>1</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>12992160804</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>l:1569964354718443</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ag:120259623620270537</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Transf. Intern. | Banner | Mulheres na Escada</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>as:120259602865020537</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lookalike Inscritos</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>c:120259602864830537</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Pareto | Lorena | Lead ads | Medicina | 26.2 | Transferência Internacional</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>f:2296658154476727</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>LORENA - Medicina - Transf.Internacional 07/2026</t>
+        </is>
+      </c>
+      <c r="K7" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>ig</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Mariana Rodrigues</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>marianaferrazmed@gmail.com</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>5577991035705</v>
+      </c>
+      <c r="Q7" t="b">
+        <v>1</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>l:1084081040949887</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ag:Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>as:Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>c:Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>f:1840466290646742</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>LORENA - Regulares | TO 07/2026</t>
+        </is>
+      </c>
+      <c r="K8" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>ig</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Wanessa Soares Oliveira</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>wany_so@yahoo.com.br</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="b">
+        <v>1</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>p:+5512997599450</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>l:1585426373309030</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ag:Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>as:Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>c:Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>f:1840466290646742</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>LORENA - Regulares | TO 07/2026</t>
+        </is>
+      </c>
+      <c r="K9" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>fb</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Rosemire Ferraz</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>rosemireferraz@hotmail.com</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="b">
+        <v>1</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>p:+5512997443979</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>l:1038643005207473</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ag:120256117818500405</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Terapia Ocupacional | Banner | Brinquedos</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>as:120256116659800405</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lookalike Matriculados</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>c:120256116659790405</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Pareto | Lead Ads | Canaã - TO</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>f:2098557274428904</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Canaã - Regulares | TO 07/2026</t>
+        </is>
+      </c>
+      <c r="K10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>ig</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>adriana.costa33@yahoo.com</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>5591993968334</v>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Adriana Costa</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>l:4262813970697647</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ag:120256117818500405</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Terapia Ocupacional | Banner | Brinquedos</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>as:120256116659800405</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Lookalike Matriculados</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>c:120256116659790405</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Pareto | Lead Ads | Canaã - TO</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>f:2098557274428904</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Canaã - Regulares | TO 07/2026</t>
+        </is>
+      </c>
+      <c r="K11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>ig</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>michele.n.silva6@aluno.senai.br</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>5591993888668</v>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Michele Silva</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>l:1377810127008404</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ag:120256117818500405</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Terapia Ocupacional | Banner | Brinquedos</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>as:120256116659800405</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Lookalike Matriculados</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>c:120256116659790405</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Pareto | Lead Ads | Canaã - TO</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>f:2098557274428904</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Canaã - Regulares | TO 07/2026</t>
+        </is>
+      </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>ig</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>eumarianabatista2008@gmail.com</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>5594991134938</v>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Mariana vitória pinto batista</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/novos_leads.xlsx
+++ b/novos_leads.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -535,11 +535,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>l:4635658106654998</t>
+          <t>l:1797392471396738</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46239</v>
+        <v>46245</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -593,11 +593,11 @@
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
-          <t>mariaclaudialimaferreira9@gmail.com</t>
+          <t>carmemluciapereira052011@hotmail.com</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>5512991243122</v>
+        <v>5531985500460</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>Maria Claudia</t>
+          <t>Carmen</t>
         </is>
       </c>
       <c r="T2" t="b">
@@ -619,11 +619,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>l:2609020686183293</t>
+          <t>l:1627305888956848</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46238</v>
+        <v>46245</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -670,18 +670,18 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>ig</t>
+          <t>fb</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>tcristinaprincesa@gmail.com</t>
+          <t>cirineiasilva55@gmail.com</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>5535998243081</v>
+        <v>553186601733</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>Teresa Cristina De Macedo</t>
+          <t>Cirineia Rosário</t>
         </is>
       </c>
       <c r="T3" t="b">
@@ -703,50 +703,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>l:1547628913721293</t>
+          <t>l:4637171823196727</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46239</v>
+        <v>46245</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ag:Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+          <t>ag:120249230124020610</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+          <t>Terapia Ocupacional | Banner | Duas Mulheres</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>as:Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+          <t>as:120249229519180610</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+          <t>Lookalike Matriculados | LoginCRM</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>c:Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+          <t>c:120249229519170610</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+          <t>Pareto | Itabirito | Leads Ads | Regulares | 26.2 - TO</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>f:1149489480748786</t>
+          <t>f:27688517784091361</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>LORENA - Cursos Livres | 07/2026</t>
+          <t>Itabirito - Regulares | TO 07/2026</t>
         </is>
       </c>
       <c r="K4" t="b">
@@ -757,86 +757,80 @@
           <t>ig</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Técnicas emersão orofacial</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>𝑫𝒂𝒏𝒊𝒆𝒍 𝑯𝒆𝒓𝒏𝒂𝒏𝒅𝒆𝒔</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>nielhernandes204@gmail.com</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="b">
+          <t>marciaavm25@gmail.com</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>5531992839925</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Marcia Paiva Oliveira</t>
+        </is>
+      </c>
+      <c r="T4" t="b">
         <v>1</v>
       </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>5512991538409</t>
-        </is>
-      </c>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>l:988809387537755</t>
+          <t>l:3687099968111126</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46239</v>
+        <v>46245</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ag:Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+          <t>ag:120249230124020610</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+          <t>Terapia Ocupacional | Banner | Duas Mulheres</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>as:Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+          <t>as:120249229519180610</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+          <t>Lookalike Matriculados | LoginCRM</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>c:Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+          <t>c:120249229519170610</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+          <t>Pareto | Itabirito | Leads Ads | Regulares | 26.2 - TO</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>f:1149489480748786</t>
+          <t>f:27688517784091361</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>LORENA - Cursos Livres | 07/2026</t>
+          <t>Itabirito - Regulares | TO 07/2026</t>
         </is>
       </c>
       <c r="K5" t="b">
@@ -847,86 +841,80 @@
           <t>ig</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>imersão em HOF</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Leticia Dias</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>diasleticia531@gmail.com</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="b">
+          <t>mariasilava106@gmail.com</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>5531989018042</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Maria Silva</t>
+        </is>
+      </c>
+      <c r="T5" t="b">
         <v>1</v>
       </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>5512996449688</t>
-        </is>
-      </c>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>l:2651632011939417</t>
+          <t>l:1054720907205247</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46239</v>
+        <v>46245</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ag:Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+          <t>ag:120249230124020610</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+          <t>Terapia Ocupacional | Banner | Duas Mulheres</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>as:Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+          <t>as:120249229519180610</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+          <t>Lookalike Matriculados | LoginCRM</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>c:Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+          <t>c:120249229519170610</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+          <t>Pareto | Itabirito | Leads Ads | Regulares | 26.2 - TO</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>f:1149489480748786</t>
+          <t>f:27688517784091361</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>LORENA - Cursos Livres | 07/2026</t>
+          <t>Itabirito - Regulares | TO 07/2026</t>
         </is>
       </c>
       <c r="K6" t="b">
@@ -937,86 +925,80 @@
           <t>ig</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Chics Modas | Atacado de Roupas</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>clararmarques@hotmail.com</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="b">
+          <t>kattyclimadepaula@gmail.com</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>5531993228520</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>katty Cristina Lima de Paula</t>
+        </is>
+      </c>
+      <c r="T6" t="b">
         <v>1</v>
       </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>12992160804</t>
-        </is>
-      </c>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>l:1569964354718443</t>
+          <t>l:1568679161623689</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46238</v>
+        <v>46244</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ag:120259623620270537</t>
+          <t>ag:120249230124020610</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Transf. Intern. | Banner | Mulheres na Escada</t>
+          <t>Terapia Ocupacional | Banner | Duas Mulheres</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>as:120259602865020537</t>
+          <t>as:120249229519180610</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lookalike Inscritos</t>
+          <t>Lookalike Matriculados | LoginCRM</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>c:120259602864830537</t>
+          <t>c:120249229519170610</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pareto | Lorena | Lead ads | Medicina | 26.2 | Transferência Internacional</t>
+          <t>Pareto | Itabirito | Leads Ads | Regulares | 26.2 - TO</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>f:2296658154476727</t>
+          <t>f:27688517784091361</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>LORENA - Medicina - Transf.Internacional 07/2026</t>
+          <t>Itabirito - Regulares | TO 07/2026</t>
         </is>
       </c>
       <c r="K7" t="b">
@@ -1028,79 +1010,79 @@
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Mariana Rodrigues</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>marianaferrazmed@gmail.com</t>
+          <t>lanalopes68@gmail.com</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>5577991035705</v>
-      </c>
-      <c r="Q7" t="b">
+        <v>5531995654142</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Lanna Lopes Lopes</t>
+        </is>
+      </c>
+      <c r="T7" t="b">
         <v>1</v>
       </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>l:1084081040949887</t>
+          <t>l:2465837527230228</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46239</v>
+        <v>46244</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ag:Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+          <t>ag:120249230124020610</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+          <t>Terapia Ocupacional | Banner | Duas Mulheres</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>as:Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+          <t>as:120249229519180610</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+          <t>Lookalike Matriculados | LoginCRM</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>c:Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+          <t>c:120249229519170610</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+          <t>Pareto | Itabirito | Leads Ads | Regulares | 26.2 - TO</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>f:1840466290646742</t>
+          <t>f:27688517784091361</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>LORENA - Regulares | TO 07/2026</t>
+          <t>Itabirito - Regulares | TO 07/2026</t>
         </is>
       </c>
       <c r="K8" t="b">
@@ -1112,81 +1094,79 @@
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Wanessa Soares Oliveira</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>wany_so@yahoo.com.br</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="b">
+          <t>solanja@yahoo.com.br</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>553199537416</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>solanja Batista de Carvalho</t>
+        </is>
+      </c>
+      <c r="T8" t="b">
         <v>1</v>
       </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>p:+5512997599450</t>
-        </is>
-      </c>
+      <c r="V8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>l:1585426373309030</t>
+          <t>l:1032210029433699</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>46238</v>
+        <v>46244</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ag:Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+          <t>ag:120249230124020610</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+          <t>Terapia Ocupacional | Banner | Duas Mulheres</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>as:Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+          <t>as:120249229519180610</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+          <t>Lookalike Matriculados | LoginCRM</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>c:Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+          <t>c:120249229519170610</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+          <t>Pareto | Itabirito | Leads Ads | Regulares | 26.2 - TO</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>f:1840466290646742</t>
+          <t>f:27688517784091361</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>LORENA - Regulares | TO 07/2026</t>
+          <t>Itabirito - Regulares | TO 07/2026</t>
         </is>
       </c>
       <c r="K9" t="b">
@@ -1194,85 +1174,83 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>fb</t>
+          <t>ig</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Rosemire Ferraz</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
-          <t>rosemireferraz@hotmail.com</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="b">
+          <t>josielef18@gmail.com</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>5531989103492</v>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Josiele Fernandes</t>
+        </is>
+      </c>
+      <c r="T9" t="b">
         <v>1</v>
       </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>p:+5512997443979</t>
-        </is>
-      </c>
+      <c r="V9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>l:1038643005207473</t>
+          <t>l:4524947071096451</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>46238</v>
+        <v>46244</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ag:120256117818500405</t>
+          <t>ag:120249230124020610</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Terapia Ocupacional | Banner | Brinquedos</t>
+          <t>Terapia Ocupacional | Banner | Duas Mulheres</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>as:120256116659800405</t>
+          <t>as:120249229519180610</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lookalike Matriculados</t>
+          <t>Lookalike Matriculados | LoginCRM</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>c:120256116659790405</t>
+          <t>c:120249229519170610</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Pareto | Lead Ads | Canaã - TO</t>
+          <t>Pareto | Itabirito | Leads Ads | Regulares | 26.2 - TO</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>f:2098557274428904</t>
+          <t>f:27688517784091361</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Canaã - Regulares | TO 07/2026</t>
+          <t>Itabirito - Regulares | TO 07/2026</t>
         </is>
       </c>
       <c r="K10" t="b">
@@ -1287,11 +1265,11 @@
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
-          <t>adriana.costa33@yahoo.com</t>
+          <t>claudia.honorato@edu.pbh.gov.br</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>5591993968334</v>
+        <v>5531971329163</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -1301,60 +1279,62 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>Adriana Costa</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr"/>
+          <t>Hono Clau</t>
+        </is>
+      </c>
+      <c r="T10" t="b">
+        <v>1</v>
+      </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>l:4262813970697647</t>
+          <t>l:1443904297565115</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>46238</v>
+        <v>46244</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ag:120256117818500405</t>
+          <t>ag:120249230124020610</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Terapia Ocupacional | Banner | Brinquedos</t>
+          <t>Terapia Ocupacional | Banner | Duas Mulheres</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>as:120256116659800405</t>
+          <t>as:120249229519180610</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lookalike Matriculados</t>
+          <t>Lookalike Matriculados | LoginCRM</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>c:120256116659790405</t>
+          <t>c:120249229519170610</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Pareto | Lead Ads | Canaã - TO</t>
+          <t>Pareto | Itabirito | Leads Ads | Regulares | 26.2 - TO</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>f:2098557274428904</t>
+          <t>f:27688517784091361</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Canaã - Regulares | TO 07/2026</t>
+          <t>Itabirito - Regulares | TO 07/2026</t>
         </is>
       </c>
       <c r="K11" t="b">
@@ -1362,18 +1342,18 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>ig</t>
+          <t>fb</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
-          <t>michele.n.silva6@aluno.senai.br</t>
+          <t>ritamentor@yahoo.com.br</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>5591993888668</v>
+        <v>31987675875</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -1383,60 +1363,62 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>Michele Silva</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr"/>
+          <t>Rita Mentor</t>
+        </is>
+      </c>
+      <c r="T11" t="b">
+        <v>1</v>
+      </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>l:1377810127008404</t>
+          <t>l:1028635236831963</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>46238</v>
+        <v>46244</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ag:120256117818500405</t>
+          <t>ag:120249230124020610</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Terapia Ocupacional | Banner | Brinquedos</t>
+          <t>Terapia Ocupacional | Banner | Duas Mulheres</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>as:120256116659800405</t>
+          <t>as:120249229519180610</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lookalike Matriculados</t>
+          <t>Lookalike Matriculados | LoginCRM</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>c:120256116659790405</t>
+          <t>c:120249229519170610</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Pareto | Lead Ads | Canaã - TO</t>
+          <t>Pareto | Itabirito | Leads Ads | Regulares | 26.2 - TO</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>f:2098557274428904</t>
+          <t>f:27688517784091361</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Canaã - Regulares | TO 07/2026</t>
+          <t>Itabirito - Regulares | TO 07/2026</t>
         </is>
       </c>
       <c r="K12" t="b">
@@ -1451,11 +1433,11 @@
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
-          <t>eumarianabatista2008@gmail.com</t>
+          <t>adalima04@yahoo.com.br</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>5594991134938</v>
+        <v>553199154609</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -1465,12 +1447,2750 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>Mariana vitória pinto batista</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr"/>
+          <t>Ada Lima</t>
+        </is>
+      </c>
+      <c r="T12" t="b">
+        <v>1</v>
+      </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>l:2050290312254272</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ag:120249230124020610</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Terapia Ocupacional | Banner | Duas Mulheres</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>as:120249229519180610</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Lookalike Matriculados | LoginCRM</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>c:120249229519170610</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Pareto | Itabirito | Leads Ads | Regulares | 26.2 - TO</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>f:27688517784091361</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Itabirito - Regulares | TO 07/2026</t>
+        </is>
+      </c>
+      <c r="K13" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>fb</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>terezinhajedusdarocha@gmail.com</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>553195395055</v>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Terezinha  jesus da Rocha</t>
+        </is>
+      </c>
+      <c r="T13" t="b">
+        <v>1</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>l:1910039066334018</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ag:120249230124020610</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Terapia Ocupacional | Banner | Duas Mulheres</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>as:120249229519180610</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Lookalike Matriculados | LoginCRM</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>c:120249229519170610</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Pareto | Itabirito | Leads Ads | Regulares | 26.2 - TO</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>f:27688517784091361</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Itabirito - Regulares | TO 07/2026</t>
+        </is>
+      </c>
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>fb</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>neuza13.barcelos@gmail.com</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>553182486519</v>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Neuza Barcelos Barcelos</t>
+        </is>
+      </c>
+      <c r="T14" t="b">
+        <v>1</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>l:1053121854317835</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ag:120249230124020610</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Terapia Ocupacional | Banner | Duas Mulheres</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>as:120249229519180610</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Lookalike Matriculados | LoginCRM</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>c:120249229519170610</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Pareto | Itabirito | Leads Ads | Regulares | 26.2 - TO</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>f:27688517784091361</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Itabirito - Regulares | TO 07/2026</t>
+        </is>
+      </c>
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>ig</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>codatoaliane@gmail.com</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>5531989116216</v>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Aliane Lopes</t>
+        </is>
+      </c>
+      <c r="T15" t="b">
+        <v>1</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>l:1191841153152575</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ag:120249230124020610</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Terapia Ocupacional | Banner | Duas Mulheres</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>as:120249229519180610</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Lookalike Matriculados | LoginCRM</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>c:120249229519170610</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Pareto | Itabirito | Leads Ads | Regulares | 26.2 - TO</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>f:27688517784091361</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Itabirito - Regulares | TO 07/2026</t>
+        </is>
+      </c>
+      <c r="K16" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>ig</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>dangelamaria515@gmail.com</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>5521965953509</v>
+      </c>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>Angela Maria dos Santos</t>
+        </is>
+      </c>
+      <c r="T16" t="b">
+        <v>1</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>l:1062684289469787</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ag:120259623620270537</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Transf. Intern. | Banner | Mulheres na Escada</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>as:120259602865020537</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Lookalike Inscritos</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>c:120259602864830537</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Pareto | Lorena | Lead ads | Medicina | 26.2 | Transferência Internacional</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>f:2296658154476727</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>LORENA - Medicina - Transf.Internacional 07/2026</t>
+        </is>
+      </c>
+      <c r="K17" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>ig</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Julia Matias</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>juliamcdiniz@hotmail.com</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>5543991745335</v>
+      </c>
+      <c r="Q17" t="b">
+        <v>1</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>l:1612806486873712</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ag:120259623620270537</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Transf. Intern. | Banner | Mulheres na Escada</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>as:120259602865020537</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Lookalike Inscritos</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>c:120259602864830537</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Pareto | Lorena | Lead ads | Medicina | 26.2 | Transferência Internacional</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>f:2296658154476727</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>LORENA - Medicina - Transf.Internacional 07/2026</t>
+        </is>
+      </c>
+      <c r="K18" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>ig</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Maria Clara Braz</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>mclarafersz@gmail.com</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>16992705548</v>
+      </c>
+      <c r="Q18" t="b">
+        <v>1</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>l:1075384594942193</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ag:120259623620270537</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Transf. Intern. | Banner | Mulheres na Escada</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>as:120259602865020537</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Lookalike Inscritos</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>c:120259602864830537</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Pareto | Lorena | Lead ads | Medicina | 26.2 | Transferência Internacional</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>f:2296658154476727</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>LORENA - Medicina - Transf.Internacional 07/2026</t>
+        </is>
+      </c>
+      <c r="K19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>ig</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Luana Sena | • Estudante de Medicina</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>lueds2@yahoo.com.br</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>5591980899701</v>
+      </c>
+      <c r="Q19" t="b">
+        <v>1</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>l:1098135026098813</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ag:120259623620270537</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Transf. Intern. | Banner | Mulheres na Escada</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>as:120259602865020537</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Lookalike Inscritos</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>c:120259602864830537</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Pareto | Lorena | Lead ads | Medicina | 26.2 | Transferência Internacional</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>f:2296658154476727</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>LORENA - Medicina - Transf.Internacional 07/2026</t>
+        </is>
+      </c>
+      <c r="K20" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>fb</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Gabriel Reis</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>admprojetovida@gmail.com</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>5511972304806</v>
+      </c>
+      <c r="Q20" t="b">
+        <v>1</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>l:987364504331677</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ag:120259623620270537</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Transf. Intern. | Banner | Mulheres na Escada</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>as:120259602865020537</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Lookalike Inscritos</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>c:120259602864830537</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Pareto | Lorena | Lead ads | Medicina | 26.2 | Transferência Internacional</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>f:2296658154476727</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>LORENA - Medicina - Transf.Internacional 07/2026</t>
+        </is>
+      </c>
+      <c r="K21" t="b">
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>ig</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Marcelo Neves</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>marceloneves2507@gmail.com</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>5522997285071</v>
+      </c>
+      <c r="Q21" t="b">
+        <v>1</v>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>l:2117452708844216</t>
+        </is>
+      </c>
+      <c r="B22" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ag:120259623620270537</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Transf. Intern. | Banner | Mulheres na Escada</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>as:120259602865020537</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lookalike Inscritos</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>c:120259602864830537</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Pareto | Lorena | Lead ads | Medicina | 26.2 | Transferência Internacional</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>f:2296658154476727</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>LORENA - Medicina - Transf.Internacional 07/2026</t>
+        </is>
+      </c>
+      <c r="K22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>ig</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Leandro</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>segurocard@gmail.com</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>5511976457656</v>
+      </c>
+      <c r="Q22" t="b">
+        <v>1</v>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>l:1623090099529493</t>
+        </is>
+      </c>
+      <c r="B23" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ag:120259623620270537</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Transf. Intern. | Banner | Mulheres na Escada</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>as:120259602865020537</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Lookalike Inscritos</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>c:120259602864830537</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Pareto | Lorena | Lead ads | Medicina | 26.2 | Transferência Internacional</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>f:2296658154476727</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>LORENA - Medicina - Transf.Internacional 07/2026</t>
+        </is>
+      </c>
+      <c r="K23" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>ig</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Marcella Rocha</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>marcellaprado274@gmail.com</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>16892945965</v>
+      </c>
+      <c r="Q23" t="b">
+        <v>1</v>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>l:2101121227460090</t>
+        </is>
+      </c>
+      <c r="B24" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ag:120259623620270537</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Transf. Intern. | Banner | Mulheres na Escada</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>as:120259602865020537</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Lookalike Inscritos</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>c:120259602864830537</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Pareto | Lorena | Lead ads | Medicina | 26.2 | Transferência Internacional</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>f:2296658154476727</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>LORENA - Medicina - Transf.Internacional 07/2026</t>
+        </is>
+      </c>
+      <c r="K24" t="b">
+        <v>0</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>fb</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Ricardo Portugal</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>ricardoaportugal2@gmail.com</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>553391513980</v>
+      </c>
+      <c r="Q24" t="b">
+        <v>1</v>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>l:1709409180169618</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ag:120259623620270537</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Transf. Intern. | Banner | Mulheres na Escada</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>as:120259602865020537</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Lookalike Inscritos</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>c:120259602864830537</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Pareto | Lorena | Lead ads | Medicina | 26.2 | Transferência Internacional</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>f:2296658154476727</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>LORENA - Medicina - Transf.Internacional 07/2026</t>
+        </is>
+      </c>
+      <c r="K25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>ig</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Carmen Bittencourt M</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>carmen.lucya@hotmail.com</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>5567984012872</v>
+      </c>
+      <c r="Q25" t="b">
+        <v>1</v>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>l:1018008154438290</t>
+        </is>
+      </c>
+      <c r="B26" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ag:Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>as:Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>c:Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Você não tem permissão suficiente. Consulte esta ajuda: https://www.facebook.com/business/help/766393076839635</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>f:1840466290646742</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>LORENA - Regulares | TO 07/2026</t>
+        </is>
+      </c>
+      <c r="K26" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>ig</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Fer Nanda Santos</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>falecomnanda@yahoo.com.br</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="b">
+        <v>1</v>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>p:+5512988077580</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>l:1377560537036330</t>
+        </is>
+      </c>
+      <c r="B27" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ag:120256117818500405</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Terapia Ocupacional | Banner | Brinquedos</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>as:120256116659800405</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Lookalike Matriculados</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>c:120256116659790405</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Pareto | Lead Ads | Canaã - TO</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>f:2098557274428904</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Canaã - Regulares | TO 07/2026</t>
+        </is>
+      </c>
+      <c r="K27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>fb</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>larinevieira74@gmail.com</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>5594981197292</v>
+      </c>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>Larine Vieira</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>l:1791717738943618</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ag:120256117818500405</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Terapia Ocupacional | Banner | Brinquedos</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>as:120256116659800405</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Lookalike Matriculados</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>c:120256116659790405</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Pareto | Lead Ads | Canaã - TO</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>f:2098557274428904</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Canaã - Regulares | TO 07/2026</t>
+        </is>
+      </c>
+      <c r="K28" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>fb</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>oliveirajosias416@gmail.com</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>5596984112023</v>
+      </c>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>Josias Oliveira</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>l:1911693069807632</t>
+        </is>
+      </c>
+      <c r="B29" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ag:120256117818500405</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Terapia Ocupacional | Banner | Brinquedos</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>as:120256116659800405</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Lookalike Matriculados</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>c:120256116659790405</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Pareto | Lead Ads | Canaã - TO</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>f:2098557274428904</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Canaã - Regulares | TO 07/2026</t>
+        </is>
+      </c>
+      <c r="K29" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>ig</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>eunice.sv75@gmail.com</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>5594992292976</v>
+      </c>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>Eunice Sousa Viana</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>l:1402542448468856</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ag:120256117818500405</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Terapia Ocupacional | Banner | Brinquedos</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>as:120256116659800405</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Lookalike Matriculados</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>c:120256116659790405</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Pareto | Lead Ads | Canaã - TO</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>f:2098557274428904</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Canaã - Regulares | TO 07/2026</t>
+        </is>
+      </c>
+      <c r="K30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>fb</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>fb_rangelms@hotmail.com</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>5598981311606</v>
+      </c>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>Fábio Rangel</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>l:1034922185808062</t>
+        </is>
+      </c>
+      <c r="B31" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ag:120256117818500405</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Terapia Ocupacional | Banner | Brinquedos</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>as:120256116659800405</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Lookalike Matriculados</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>c:120256116659790405</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Pareto | Lead Ads | Canaã - TO</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>f:2098557274428904</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Canaã - Regulares | TO 07/2026</t>
+        </is>
+      </c>
+      <c r="K31" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>fb</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>laulima409@gmail.com</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>5591993891760</v>
+      </c>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>Lau Lima</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>l:948687531604446</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ag:120256117818500405</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Terapia Ocupacional | Banner | Brinquedos</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>as:120256116659800405</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Lookalike Matriculados</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>c:120256116659790405</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Pareto | Lead Ads | Canaã - TO</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>f:2098557274428904</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Canaã - Regulares | TO 07/2026</t>
+        </is>
+      </c>
+      <c r="K32" t="b">
+        <v>0</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>ig</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>sandrasaga2020@gmail.com</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>5563991027214</v>
+      </c>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>Sandra Pereira de Oliveira</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>l:1059423513250235</t>
+        </is>
+      </c>
+      <c r="B33" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ag:120256117818500405</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Terapia Ocupacional | Banner | Brinquedos</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>as:120256116659800405</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Lookalike Matriculados</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>c:120256116659790405</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Pareto | Lead Ads | Canaã - TO</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>f:2098557274428904</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Canaã - Regulares | TO 07/2026</t>
+        </is>
+      </c>
+      <c r="K33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>fb</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>franciscatiana75@gmail.com</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>5594992325479</v>
+      </c>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>Francisca Cristiane Neres da Silva</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>l:1346107007606980</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ag:120256117818500405</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Terapia Ocupacional | Banner | Brinquedos</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>as:120256116659800405</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Lookalike Matriculados</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>c:120256116659790405</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Pareto | Lead Ads | Canaã - TO</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>f:2098557274428904</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Canaã - Regulares | TO 07/2026</t>
+        </is>
+      </c>
+      <c r="K34" t="b">
+        <v>0</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>ig</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>eliane.saraivali19@gmail.com</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>5594992771472</v>
+      </c>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>Liane Lima</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>l:985883987796456</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ag:120256117818500405</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Terapia Ocupacional | Banner | Brinquedos</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>as:120256116659800405</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Lookalike Matriculados</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>c:120256116659790405</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Pareto | Lead Ads | Canaã - TO</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>f:2098557274428904</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Canaã - Regulares | TO 07/2026</t>
+        </is>
+      </c>
+      <c r="K35" t="b">
+        <v>0</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>ig</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>natanyasaless@gmail.com</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>5594992924047</v>
+      </c>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>Natânia</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>l:1598338148470996</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>ag:120256117818500405</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Terapia Ocupacional | Banner | Brinquedos</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>as:120256116659800405</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Lookalike Matriculados</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>c:120256116659790405</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Pareto | Lead Ads | Canaã - TO</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>f:2098557274428904</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Canaã - Regulares | TO 07/2026</t>
+        </is>
+      </c>
+      <c r="K36" t="b">
+        <v>0</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>ig</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>eduardateixeiracoelho989@gmail.com</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>5594991662691</v>
+      </c>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>Eduarda Teixeira Coelho</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>l:1751333446095731</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ag:120256117818500405</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Terapia Ocupacional | Banner | Brinquedos</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>as:120256116659800405</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Lookalike Matriculados</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>c:120256116659790405</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Pareto | Lead Ads | Canaã - TO</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>f:2098557274428904</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Canaã - Regulares | TO 07/2026</t>
+        </is>
+      </c>
+      <c r="K37" t="b">
+        <v>0</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>ig</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>josianematos2@gmail.com</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>5591981597724</v>
+      </c>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>Josiane Andrade</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>l:1077423858269594</t>
+        </is>
+      </c>
+      <c r="B38" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>ag:120256117818500405</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Terapia Ocupacional | Banner | Brinquedos</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>as:120256116659800405</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Lookalike Matriculados</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>c:120256116659790405</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Pareto | Lead Ads | Canaã - TO</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>f:2098557274428904</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Canaã - Regulares | TO 07/2026</t>
+        </is>
+      </c>
+      <c r="K38" t="b">
+        <v>0</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>fb</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>nms_carlinhos@hotmail.com</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>5594991839622</v>
+      </c>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>Carlinhos Santos</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>l:1740540430570525</t>
+        </is>
+      </c>
+      <c r="B39" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>ag:120256117818500405</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Terapia Ocupacional | Banner | Brinquedos</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>as:120256116659800405</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Lookalike Matriculados</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>c:120256116659790405</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Pareto | Lead Ads | Canaã - TO</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>f:2098557274428904</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Canaã - Regulares | TO 07/2026</t>
+        </is>
+      </c>
+      <c r="K39" t="b">
+        <v>0</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>ig</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>queilaapae@gmail.com</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>5594991025192</v>
+      </c>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>Queila Andreia Carvalho</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>l:2493466994494247</t>
+        </is>
+      </c>
+      <c r="B40" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>ag:120256117818500405</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Terapia Ocupacional | Banner | Brinquedos</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>as:120256116659800405</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Lookalike Matriculados</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>c:120256116659790405</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Pareto | Lead Ads | Canaã - TO</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>f:2098557274428904</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Canaã - Regulares | TO 07/2026</t>
+        </is>
+      </c>
+      <c r="K40" t="b">
+        <v>0</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>ig</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>taysonsilva1978@gmail.com</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>5594991107886</v>
+      </c>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>Tayson Silva</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>l:2251242539064386</t>
+        </is>
+      </c>
+      <c r="B41" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>ag:120256117818500405</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Terapia Ocupacional | Banner | Brinquedos</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>as:120256116659800405</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Lookalike Matriculados</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>c:120256116659790405</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Pareto | Lead Ads | Canaã - TO</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>f:2098557274428904</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Canaã - Regulares | TO 07/2026</t>
+        </is>
+      </c>
+      <c r="K41" t="b">
+        <v>0</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>fb</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>eldaamadoralves@gmail.com</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>5563992182859</v>
+      </c>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>Elda Amador Alves</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>l:1438672241408082</t>
+        </is>
+      </c>
+      <c r="B42" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ag:120256117818500405</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Terapia Ocupacional | Banner | Brinquedos</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>as:120256116659800405</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Lookalike Matriculados</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>c:120256116659790405</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Pareto | Lead Ads | Canaã - TO</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>f:2098557274428904</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Canaã - Regulares | TO 07/2026</t>
+        </is>
+      </c>
+      <c r="K42" t="b">
+        <v>0</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>fb</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>salvianejms10@gmail.com</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>5594991600247</v>
+      </c>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>Ane Nascimento</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>l:3192492714294933</t>
+        </is>
+      </c>
+      <c r="B43" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ag:120256117818500405</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Terapia Ocupacional | Banner | Brinquedos</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>as:120256116659800405</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Lookalike Matriculados</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>c:120256116659790405</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Pareto | Lead Ads | Canaã - TO</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>f:2098557274428904</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Canaã - Regulares | TO 07/2026</t>
+        </is>
+      </c>
+      <c r="K43" t="b">
+        <v>0</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>ig</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>karolynesoares944@gmail.com</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>5563984849764</v>
+      </c>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>Karoliny De Andrade Soares</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>l:885939014296780</t>
+        </is>
+      </c>
+      <c r="B44" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ag:120256117818500405</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Terapia Ocupacional | Banner | Brinquedos</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>as:120256116659800405</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Lookalike Matriculados</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>c:120256116659790405</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Pareto | Lead Ads | Canaã - TO</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>f:2098557274428904</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Canaã - Regulares | TO 07/2026</t>
+        </is>
+      </c>
+      <c r="K44" t="b">
+        <v>0</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>ig</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>layanemedeiros117@gmail.com</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>5594991250835</v>
+      </c>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>l:3918774048431210</t>
+        </is>
+      </c>
+      <c r="B45" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>ag:120256117818500405</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Terapia Ocupacional | Banner | Brinquedos</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>as:120256116659800405</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Lookalike Matriculados</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>c:120256116659790405</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Pareto | Lead Ads | Canaã - TO</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>f:2098557274428904</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Canaã - Regulares | TO 07/2026</t>
+        </is>
+      </c>
+      <c r="K45" t="b">
+        <v>0</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>ig</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>limavaldylene3@gmail.com</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>5594991563998</v>
+      </c>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>João Guilherme Da Silva Ribeiro</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/novos_leads.xlsx
+++ b/novos_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,6 +442,11 @@
           <t>unidadeform</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Landing Page ou Formulário de Origem</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -469,6 +474,11 @@
           <t>Medicina Lorena</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Medicina - Formulário Meta</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -496,6 +506,11 @@
           <t>Canaã</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ARQ - Formulário Meta</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -521,6 +536,11 @@
       <c r="E4" t="inlineStr">
         <is>
           <t>Canaã</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>AGR - Formulário Meta</t>
         </is>
       </c>
     </row>

--- a/novos_leads.xlsx
+++ b/novos_leads.xlsx
@@ -419,17 +419,17 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>nome_completo</t>
+          <t>Nome Completo</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>telefone</t>
+          <t>Telefone Celular</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -439,7 +439,7 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>unidadeform</t>
+          <t>Unidadeform (crmeduc_unidadeform)</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">

--- a/novos_leads.xlsx
+++ b/novos_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,94 +451,126 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Wellington Garbin</t>
+          <t>Alhandra Coelho Coelho</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>garbindapururuca@bol.com.br</t>
+          <t>alhandracoelho@hotmail.com</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>5518981830032</t>
+          <t>31973595841</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>lorena - medicina - transf.internacional 07/2026</t>
+          <t>itabirito - regulares | to 07/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Medicina Lorena</t>
+          <t>Itabirito</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Medicina - Formulário Meta</t>
+          <t>TO - Formulário Meta</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Henrique Campos</t>
+          <t>PatyFe Oliveira Cordeiro</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>carloshenriquebritodasilvab@gmail.com</t>
+          <t>patyoliverl_21@hotmail.com</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>5594991524649</t>
+          <t>5512981229239</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>canaã - regulares | arquitetura  08/2026</t>
+          <t>lorena - regulares | to 07/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Canaã</t>
+          <t>Lorena</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ARQ - Formulário Meta</t>
+          <t>TO - Formulário Meta</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bianca Sousa</t>
+          <t>Solange Jorge Lima</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>biancasousa3708@gmail.com</t>
+          <t>solangejlima@yahoo.com.br</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>559492309285</t>
+          <t>5512981673308</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>lorena - regulares | to 07/2026</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>TO - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Ok Francisca Barbosa Ferreira</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>francisca9090barbosa@gmail.com</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>5594992664524</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>canaã - regulares | agronomia 08/2026</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Canaã</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>AGR - Formulário Meta</t>
         </is>

--- a/novos_leads.xlsx
+++ b/novos_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,17 +451,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alhandra Coelho Coelho</t>
+          <t>Aderivania Ferreira</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>alhandracoelho@hotmail.com</t>
+          <t>aderivaniaf@yahoo.com</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>31973595841</t>
+          <t>5531973120183</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -483,27 +483,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PatyFe Oliveira Cordeiro</t>
+          <t>Silvana Ribeiro</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>patyoliverl_21@hotmail.com</t>
+          <t>syll04@hotmail.com</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>5512981229239</t>
+          <t>5531983873969</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>lorena - regulares | to 07/2026</t>
+          <t>itabirito - regulares | to 07/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Lorena</t>
+          <t>Itabirito</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -515,27 +515,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Solange Jorge Lima</t>
+          <t>Erenis Lima Carvalho</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>solangejlima@yahoo.com.br</t>
+          <t>erenislimac@gmail.com</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>5512981673308</t>
+          <t>5531998125450</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>lorena - regulares | to 07/2026</t>
+          <t>itabirito - regulares | to 07/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lorena</t>
+          <t>Itabirito</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -547,32 +547,1088 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ok Francisca Barbosa Ferreira</t>
+          <t>𝕄𝔸𝕋𝕀𝔸𝕊 ℝ𝔸𝔽𝔸𝔼𝕃</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>francisca9090barbosa@gmail.com</t>
+          <t>reismatias@outlook.com</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5594992664524</t>
+          <t>5535998404677</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>itabirito - regulares | to 07/2026</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Itabirito</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>TO - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Marilene Souza</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>lena.desouzafreitas@hotmail.com</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>5532998251904</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>itabirito - regulares | to 07/2026</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Itabirito</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>TO - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Nadir Siqueira</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>nadirsiqueira2016@gmail.com</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>5532984629489</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>itabirito - regulares | to 07/2026</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Itabirito</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>TO - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Eleni Mendes</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>elenilemos@oi.com.br</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>5531991830021</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>itabirito - regulares | to 07/2026</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Itabirito</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>TO - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Marenir Villefort</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>marenirvillefort30@gmail.com</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>5531992024929</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>itabirito - regulares | to 07/2026</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Itabirito</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>TO - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Joana Vieira</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>joanavieira2013@yahoo.com.br</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>553191068161</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>itabirito - regulares | to 07/2026</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Itabirito</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>TO - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Fran Xavier</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>fraanschimtt@gmail.com</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>5511984095609</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>lorena - medicina - transf.internacional 07/2026</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Medicina Lorena</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Medicina - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Thalia Macedo</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>macedothalia27@gmail.com</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>5577998216606</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>lorena - medicina - transf.internacional 07/2026</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Medicina Lorena</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Medicina - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Giovanna Mota</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>giovannamota_sanches@hotmail.com</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>5567998898627</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>lorena - medicina - transf.internacional 07/2026</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Medicina Lorena</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Medicina - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Maurilio Monte</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>mauriliosantosdomonte04@gmail.com</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>5593992402643</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>lorena - medicina - transf.internacional 07/2026</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Medicina Lorena</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Medicina - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Fidel Feltes Morinigo</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>feltesfidel351@gmail.com</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>595984677552</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>lorena - medicina - transf.internacional 07/2026</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Medicina Lorena</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Medicina - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>DRA. MICHELE LANUSSE | MÉDICA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>michelelanussedv@gmail.com</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>45999778080</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>lorena - medicina - transf.internacional 07/2026</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Medicina Lorena</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Medicina - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Ana Rebeka</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>anarebeka1250@hotmail.com</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>595971567170</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>lorena - medicina - transf.internacional 07/2026</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Medicina Lorena</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Medicina - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Paula Iunes</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>paula.iunes@hotmail.com</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>22981177449</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>lorena - medicina - transf.internacional 07/2026</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Medicina Lorena</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Medicina - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Deborah Assis</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>medicassis@bol.com.br</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>5512997443538</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>lorena - regulares | to 07/2026</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>TO - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>𝐄𝐥𝐢𝐳𝐚 𝐅𝐞𝐫𝐧𝐚𝐧𝐝𝐞𝐬</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>fernandeseliza2007@gmail.com</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>5512991962326</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>lorena - regulares | to 07/2026</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>TO - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Jane Macedo</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>jane.moli.mac@gmail.com</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>5512982025101</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>lorena - regulares | to 07/2026</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>TO - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Elenice Silva</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>elenicesilva843@gmail.com</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>5512997893620</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>lorena - regulares | to 07/2026</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>TO - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Bruna Ribeiro</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>bbruna2211@gmail.com</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>5512991808812</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>lorena - regulares | to 07/2026</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>TO - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Beca Soares</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>rebecasoares1422@gmail.com</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>5594991109023</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>canaã - regulares | arquitetura  08/2026</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Canaã</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>ARQ - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Edvan Lima</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ledvan512@gmail.com</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>5594992767231</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>canaã - regulares | arquitetura  08/2026</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Canaã</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>ARQ - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Chris Ventura</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>cristianneventura@hotmail.com</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>5594984511783</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
           <t>canaã - regulares | agronomia 08/2026</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Canaã</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>AGR - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Rosa Batista</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>rosinalvabatista42@gmail.com</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>5594984220163</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>canaã - regulares | agronomia 08/2026</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Canaã</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>AGR - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Marcelo Desidério</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>marcelodeziderios@gmail.com</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>559493075983</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>canaã - regulares | agronomia 08/2026</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Canaã</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>AGR - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Maria Carvalho</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>socorrorjr1010@gmail.com</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>5594981106073</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>canaã - regulares | agronomia 08/2026</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Canaã</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>AGR - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Selma Sousa</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>selminhaselma145@gmail.com</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>5594984421074</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>canaã - regulares | agronomia 08/2026</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Canaã</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>AGR - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Klenys Ruan</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>kruam1501@gmail.com</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>559491531686</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>canaã - regulares | agronomia 08/2026</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Canaã</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>AGR - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Kaylane De Sousa Santos</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>kaylanedesousa2020@gmail.com</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>559491063283</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>canaã - regulares | agronomia 08/2026</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Canaã</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>AGR - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Gerson Fonseca Filho</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>gersonoliveirasouzafilho5@gmail.com</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>5594991645826</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>canaã - regulares | agronomia 08/2026</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Canaã</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>AGR - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>neuton reis figueredo</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>neytonfigueiredoreis20@gmail.com</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>5594984079154</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>canaã - regulares | agronomia 08/2026</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Canaã</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>AGR - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Nathália Santos</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>nathaliamsantos94@gmail.com</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>5532999309826</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>canaã - regulares | to 07/2026</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Canaã</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>TO - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Ieda</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>iedanardaci@gmail.com</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>5594992742606</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>canaã - regulares | to 07/2026</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Canaã</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>TO - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>marlene pacheco</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>marlenesoarespacheco@gmail.com</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>5594984082713</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>canaã - regulares | to 07/2026</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Canaã</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>TO - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Wilson Rodrigues Ferreira</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>rodriguesferreirawilson89@gmail.com</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>5594991969439</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>canaã - regulares | to 07/2026</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Canaã</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>TO - Formulário Meta</t>
         </is>
       </c>
     </row>

--- a/novos_leads.xlsx
+++ b/novos_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -739,81 +739,81 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Fran Xavier</t>
+          <t>Magali Campos de Paula</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>fraanschimtt@gmail.com</t>
+          <t>magaldepaula@gmail.com</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5511984095609</t>
+          <t>5533999410732</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>lorena - medicina - transf.internacional 07/2026</t>
+          <t>itabirito - regulares | to 07/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Medicina Lorena</t>
+          <t>Itabirito</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Medicina - Formulário Meta</t>
+          <t>TO - Formulário Meta</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Thalia Macedo</t>
+          <t>Consolaçao Melo</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>macedothalia27@gmail.com</t>
+          <t>consolacaomelo@hotmail.com</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>5577998216606</t>
+          <t>5537999892727</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>lorena - medicina - transf.internacional 07/2026</t>
+          <t>itabirito - regulares | to 07/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Medicina Lorena</t>
+          <t>Itabirito</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Medicina - Formulário Meta</t>
+          <t>TO - Formulário Meta</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Giovanna Mota</t>
+          <t>Fran Xavier</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>giovannamota_sanches@hotmail.com</t>
+          <t>fraanschimtt@gmail.com</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>5567998898627</t>
+          <t>5511984095609</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -835,17 +835,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Maurilio Monte</t>
+          <t>Thalia Macedo</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>mauriliosantosdomonte04@gmail.com</t>
+          <t>macedothalia27@gmail.com</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>5593992402643</t>
+          <t>5577998216606</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -867,17 +867,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Fidel Feltes Morinigo</t>
+          <t>Giovanna Mota</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>feltesfidel351@gmail.com</t>
+          <t>giovannamota_sanches@hotmail.com</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>595984677552</t>
+          <t>5567998898627</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -899,17 +899,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DRA. MICHELE LANUSSE | MÉDICA</t>
+          <t>Maurilio Monte</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>michelelanussedv@gmail.com</t>
+          <t>mauriliosantosdomonte04@gmail.com</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>45999778080</t>
+          <t>5593992402643</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -931,17 +931,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ana Rebeka</t>
+          <t>Fidel Feltes Morinigo</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>anarebeka1250@hotmail.com</t>
+          <t>feltesfidel351@gmail.com</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>595971567170</t>
+          <t>595984677552</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -963,17 +963,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Paula Iunes</t>
+          <t>DRA. MICHELE LANUSSE | MÉDICA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>paula.iunes@hotmail.com</t>
+          <t>michelelanussedv@gmail.com</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>22981177449</t>
+          <t>45999778080</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -995,81 +995,81 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Deborah Assis</t>
+          <t>Ana Rebeka</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>medicassis@bol.com.br</t>
+          <t>anarebeka1250@hotmail.com</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>5512997443538</t>
+          <t>595971567170</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>lorena - regulares | to 07/2026</t>
+          <t>lorena - medicina - transf.internacional 07/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lorena</t>
+          <t>Medicina Lorena</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>TO - Formulário Meta</t>
+          <t>Medicina - Formulário Meta</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>𝐄𝐥𝐢𝐳𝐚 𝐅𝐞𝐫𝐧𝐚𝐧𝐝𝐞𝐬</t>
+          <t>Paula Iunes</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>fernandeseliza2007@gmail.com</t>
+          <t>paula.iunes@hotmail.com</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>5512991962326</t>
+          <t>22981177449</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>lorena - regulares | to 07/2026</t>
+          <t>lorena - medicina - transf.internacional 07/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lorena</t>
+          <t>Medicina Lorena</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>TO - Formulário Meta</t>
+          <t>Medicina - Formulário Meta</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Jane Macedo</t>
+          <t>Deborah Assis</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>jane.moli.mac@gmail.com</t>
+          <t>medicassis@bol.com.br</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>5512982025101</t>
+          <t>5512997443538</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1091,17 +1091,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Elenice Silva</t>
+          <t>𝐄𝐥𝐢𝐳𝐚 𝐅𝐞𝐫𝐧𝐚𝐧𝐝𝐞𝐬</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>elenicesilva843@gmail.com</t>
+          <t>fernandeseliza2007@gmail.com</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>5512997893620</t>
+          <t>5512991962326</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1123,17 +1123,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Bruna Ribeiro</t>
+          <t>Jane Macedo</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>bbruna2211@gmail.com</t>
+          <t>jane.moli.mac@gmail.com</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>5512991808812</t>
+          <t>5512982025101</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1155,150 +1155,150 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Beca Soares</t>
+          <t>Elenice Silva</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>rebecasoares1422@gmail.com</t>
+          <t>elenicesilva843@gmail.com</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>5594991109023</t>
+          <t>5512997893620</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>canaã - regulares | arquitetura  08/2026</t>
+          <t>lorena - regulares | to 07/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Canaã</t>
+          <t>Lorena</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ARQ - Formulário Meta</t>
+          <t>TO - Formulário Meta</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Edvan Lima</t>
+          <t>Bruna Ribeiro</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ledvan512@gmail.com</t>
+          <t>bbruna2211@gmail.com</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>5594992767231</t>
+          <t>5512991808812</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>canaã - regulares | arquitetura  08/2026</t>
+          <t>lorena - regulares | to 07/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Canaã</t>
+          <t>Lorena</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ARQ - Formulário Meta</t>
+          <t>TO - Formulário Meta</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Chris Ventura</t>
+          <t>Sheyla Cerqueira</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>cristianneventura@hotmail.com</t>
+          <t>sheylinhacerqueira3@gmail.com</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>5594984511783</t>
+          <t>5512981352764</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>canaã - regulares | agronomia 08/2026</t>
+          <t>lorena - regulares | to 07/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Canaã</t>
+          <t>Lorena</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AGR - Formulário Meta</t>
+          <t>TO - Formulário Meta</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rosa Batista</t>
+          <t>Estevam Rth</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>rosinalvabatista42@gmail.com</t>
+          <t>ruthbarbosaestevam@hotmail.com</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>5594984220163</t>
+          <t>5512997786607</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>canaã - regulares | agronomia 08/2026</t>
+          <t>lorena - regulares | to 07/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Canaã</t>
+          <t>Lorena</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AGR - Formulário Meta</t>
+          <t>TO - Formulário Meta</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Marcelo Desidério</t>
+          <t>Beca Soares</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>marcelodeziderios@gmail.com</t>
+          <t>rebecasoares1422@gmail.com</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>559493075983</t>
+          <t>5594991109023</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>canaã - regulares | agronomia 08/2026</t>
+          <t>canaã - regulares | arquitetura  08/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1308,29 +1308,29 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AGR - Formulário Meta</t>
+          <t>ARQ - Formulário Meta</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Maria Carvalho</t>
+          <t>Edvan Lima</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>socorrorjr1010@gmail.com</t>
+          <t>ledvan512@gmail.com</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>5594981106073</t>
+          <t>5594992767231</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>canaã - regulares | agronomia 08/2026</t>
+          <t>canaã - regulares | arquitetura  08/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1340,29 +1340,29 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>AGR - Formulário Meta</t>
+          <t>ARQ - Formulário Meta</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Selma Sousa</t>
+          <t>Gustavo 097</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>selminhaselma145@gmail.com</t>
+          <t>gustavoaraujo012.ma@gmail.com</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>5594984421074</t>
+          <t>5594984226543</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>canaã - regulares | agronomia 08/2026</t>
+          <t>canaã - regulares | arquitetura  08/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1372,24 +1372,24 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>AGR - Formulário Meta</t>
+          <t>ARQ - Formulário Meta</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Klenys Ruan</t>
+          <t>Chris Ventura</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>kruam1501@gmail.com</t>
+          <t>cristianneventura@hotmail.com</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>559491531686</t>
+          <t>5594984511783</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1411,17 +1411,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Kaylane De Sousa Santos</t>
+          <t>Rosa Batista</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>kaylanedesousa2020@gmail.com</t>
+          <t>rosinalvabatista42@gmail.com</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>559491063283</t>
+          <t>5594984220163</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1443,17 +1443,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gerson Fonseca Filho</t>
+          <t>Marcelo Desidério</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gersonoliveirasouzafilho5@gmail.com</t>
+          <t>marcelodeziderios@gmail.com</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>5594991645826</t>
+          <t>559493075983</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1475,17 +1475,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>neuton reis figueredo</t>
+          <t>Maria Carvalho</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>neytonfigueiredoreis20@gmail.com</t>
+          <t>socorrorjr1010@gmail.com</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>5594984079154</t>
+          <t>5594981106073</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1507,22 +1507,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Nathália Santos</t>
+          <t>Selma Sousa</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nathaliamsantos94@gmail.com</t>
+          <t>selminhaselma145@gmail.com</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>5532999309826</t>
+          <t>5594984421074</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>canaã - regulares | to 07/2026</t>
+          <t>canaã - regulares | agronomia 08/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1532,29 +1532,29 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>TO - Formulário Meta</t>
+          <t>AGR - Formulário Meta</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Ieda</t>
+          <t>Klenys Ruan</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>iedanardaci@gmail.com</t>
+          <t>kruam1501@gmail.com</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>5594992742606</t>
+          <t>559491531686</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>canaã - regulares | to 07/2026</t>
+          <t>canaã - regulares | agronomia 08/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1564,29 +1564,29 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>TO - Formulário Meta</t>
+          <t>AGR - Formulário Meta</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>marlene pacheco</t>
+          <t>Kaylane De Sousa Santos</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>marlenesoarespacheco@gmail.com</t>
+          <t>kaylanedesousa2020@gmail.com</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>5594984082713</t>
+          <t>559491063283</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>canaã - regulares | to 07/2026</t>
+          <t>canaã - regulares | agronomia 08/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1596,37 +1596,389 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>TO - Formulário Meta</t>
+          <t>AGR - Formulário Meta</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>Gerson Fonseca Filho</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>gersonoliveirasouzafilho5@gmail.com</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>5594991645826</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>canaã - regulares | agronomia 08/2026</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Canaã</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>AGR - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>neuton reis figueredo</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>neytonfigueiredoreis20@gmail.com</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>5594984079154</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>canaã - regulares | agronomia 08/2026</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Canaã</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>AGR - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Edna Paixão</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>dyenara8@gmail.com</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>5591984830721</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>canaã - regulares | agronomia 08/2026</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Canaã</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>AGR - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>josias silva de Jesus</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>js8852327@gmail.com</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>5594988150207</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>canaã - regulares | agronomia 08/2026</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Canaã</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>AGR - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Rosania Merces</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>rosaniadasmercessantos@gmail.com.br</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>5594991165362</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>canaã - regulares | agronomia 08/2026</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Canaã</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>AGR - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Nathália Santos</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>nathaliamsantos94@gmail.com</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>5532999309826</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>canaã - regulares | to 07/2026</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Canaã</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>TO - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Ieda</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>iedanardaci@gmail.com</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>5594992742606</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>canaã - regulares | to 07/2026</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Canaã</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>TO - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>marlene pacheco</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>marlenesoarespacheco@gmail.com</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>5594984082713</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>canaã - regulares | to 07/2026</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Canaã</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>TO - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>Wilson Rodrigues Ferreira</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>rodriguesferreirawilson89@gmail.com</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>5594991969439</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>canaã - regulares | to 07/2026</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Canaã</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Canaã</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>TO - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Rosana C. Melo</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>rosanakeilacm@gmail.com</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>5594984043394</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>canaã - regulares | to 07/2026</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Canaã</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>TO - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Gustavo Araújo Sousa</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>gustavoaraujo012.ma@gmail.com</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>5594984226543</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>canaã - regulares | to 07/2026</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Canaã</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>TO - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Franciele Gomes</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>gomesfrancilene69@gmail.com</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>5594991270738</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>canaã - regulares | to 07/2026</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Canaã</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
         <is>
           <t>TO - Formulário Meta</t>
         </is>

--- a/novos_leads.xlsx
+++ b/novos_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,17 +451,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Magali Campos de Paula</t>
+          <t>Vanusa Fernandes</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>magaldepaula@gmail.com</t>
+          <t>vanusafernandesgreg@gmail.com</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>5533999410732</t>
+          <t>5531975612963</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -483,17 +483,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Consolaçao Melo</t>
+          <t>Camila Brandão</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>consolacaomelo@hotmail.com</t>
+          <t>camila_kamilinha@live.com</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>5537999892727</t>
+          <t>5531988836718</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -515,27 +515,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sheyla Cerqueira</t>
+          <t>Cláudia Caldeira</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>sheylinhacerqueira3@gmail.com</t>
+          <t>apaidacaldeira@hotmail.com</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>5512981352764</t>
+          <t>5531995566093</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>lorena - regulares | to 07/2026</t>
+          <t>itabirito - regulares | to 07/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lorena</t>
+          <t>Itabirito</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -547,27 +547,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Estevam Rth</t>
+          <t>Delfina mariaFerreira de sena</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ruthbarbosaestevam@hotmail.com</t>
+          <t>delfinamariaferreirasenad@gmail.com</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5512997786607</t>
+          <t>5531982698672</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>lorena - regulares | to 07/2026</t>
+          <t>itabirito - regulares | to 07/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lorena</t>
+          <t>Itabirito</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -579,222 +579,1182 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Gustavo 097</t>
+          <t>Luciana Aparecida</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>gustavoaraujo012.ma@gmail.com</t>
+          <t>lucianasouza04100@gmail.com</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5594984226543</t>
+          <t>553185012972</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>canaã - regulares | arquitetura  08/2026</t>
+          <t>itabirito - regulares | to 07/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Canaã</t>
+          <t>Itabirito</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ARQ - Formulário Meta</t>
+          <t>TO - Formulário Meta</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Edna Paixão</t>
+          <t>Adilson Sousa</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>dyenara8@gmail.com</t>
+          <t>adilsonvitorp@hotmail.com</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>5591984830721</t>
+          <t>5533988063657</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>canaã - regulares | agronomia 08/2026</t>
+          <t>itabirito - regulares | to 07/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Canaã</t>
+          <t>Itabirito</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AGR - Formulário Meta</t>
+          <t>TO - Formulário Meta</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>josias silva de Jesus</t>
+          <t>Fatima Alves</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>js8852327@gmail.com</t>
+          <t>famuscafnc10@hotmail.com</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5594988150207</t>
+          <t>5531993287789</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>canaã - regulares | agronomia 08/2026</t>
+          <t>itabirito - regulares | to 07/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Canaã</t>
+          <t>Itabirito</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AGR - Formulário Meta</t>
+          <t>TO - Formulário Meta</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Rosania Merces</t>
+          <t>Marta Aparecida Prado Ribeiro</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>rosaniadasmercessantos@gmail.com.br</t>
+          <t>martaappribeiro@gmail.com.br</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>5594991165362</t>
+          <t>553198229315</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>canaã - regulares | agronomia 08/2026</t>
+          <t>itabirito - regulares | to 07/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Canaã</t>
+          <t>Itabirito</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AGR - Formulário Meta</t>
+          <t>TO - Formulário Meta</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Rosana C. Melo</t>
+          <t>Sandra Regina Antiorio</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>rosanakeilacm@gmail.com</t>
+          <t>sanluc@uol.com.br</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>5594984043394</t>
+          <t>5511981467299</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>canaã - regulares | to 07/2026</t>
+          <t>lorena - medicina - transf.internacional 07/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Canaã</t>
+          <t>Medicina Lorena</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>TO - Formulário Meta</t>
+          <t>Medicina - Formulário Meta</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Gustavo Araújo Sousa</t>
+          <t>Maria Gabriela Boher</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>gustavoaraujo012.ma@gmail.com</t>
+          <t>marigaboher@gmail.com</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5594984226543</t>
+          <t>5524999679167</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>canaã - regulares | to 07/2026</t>
+          <t>lorena - medicina - transf.internacional 07/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Canaã</t>
+          <t>Medicina Lorena</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>TO - Formulário Meta</t>
+          <t>Medicina - Formulário Meta</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Franciele Gomes</t>
+          <t>Marcella Assis</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>gomesfrancilene69@gmail.com</t>
+          <t>marcellaassis003@gmail.com</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>5594991270738</t>
+          <t>5562994058338</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>lorena - medicina - transf.internacional 07/2026</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Medicina Lorena</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Medicina - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Vinicius Teotônio Gusmão</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>viniciusteo@hotmail.com</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>5533991508585</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>lorena - medicina - transf.internacional 07/2026</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Medicina Lorena</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Medicina - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Diana de carvalho queiroz</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>dianaqueiroz.contato@gmail.com</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>5585992447410</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>lorena - medicina - transf.internacional 07/2026</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Medicina Lorena</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Medicina - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Roxania Castro</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>rox-castro@hotmail.com</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>5592994035951</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>lorena - medicina - transf.internacional 07/2026</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Medicina Lorena</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Medicina - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Verônica Reis</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>reisveronica048@gmail.com</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>5512992495613</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>lorena - regulares | to 07/2026</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>TO - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ketllin camilly dos santos oliveira</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ketllincamilly1058@gmail.com</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>5512992396305</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>lorena - regulares | to 07/2026</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>TO - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Fabricia Oliveira</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>fabriciamoreira947@gmail.com</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>5512982747506</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>lorena - regulares | to 07/2026</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>TO - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Regiane Mendes</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>regiane3538@hotmail.com</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>5512992609186</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>lorena - regulares | to 07/2026</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>TO - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Mariana Souza</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>marianacarolinepradosilva516@gmail.com</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>5512991306703</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>lorena - regulares | to 07/2026</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>TO - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Juliana Campos da Silva</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>jucampos.daniel@gmail.com</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>5535992089097</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>lorena - regulares | to 07/2026</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>TO - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Débora Martins</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>dm9742557@gmail.com</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>5512987033258</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>lorena - regulares | to 07/2026</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>TO - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Gloria Paula</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>gloriapaula971@gmail.com</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>5512996351169</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>lorena - regulares | to 07/2026</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>TO - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Mauro Santos Silva</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>maurosantossilva2999@gmail.com</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>5594984443493</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>canaã - regulares | arquitetura  08/2026</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Canaã</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>ARQ - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Rose Lopes</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>roselia.martins19@gmail.com</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>5594991563485</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>canaã - regulares | arquitetura  08/2026</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Canaã</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>ARQ - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Pedro Mendes Neto</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>mendesnetopedro@aol.com</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>5594984190720</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>canaã - regulares | agronomia 08/2026</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Canaã</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>AGR - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Edilson Venâncio</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>edilsovenancio150@gmail.com</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>5594992206811</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>canaã - regulares | agronomia 08/2026</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Canaã</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>AGR - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Elionora Ferreira de Sa</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>elionoraferreira8@gmail.com</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>5594991499810</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>canaã - regulares | agronomia 08/2026</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Canaã</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>AGR - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Sara Rocha</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>rochasara80@gmail.com</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>5594988023795</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>canaã - regulares | agronomia 08/2026</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Canaã</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>AGR - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Lina D M Souza</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Lina954@outlook.com</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>94914249737</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>canaã - regulares | agronomia 08/2026</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Canaã</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>AGR - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Rita Ferreira De Sousa</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ritaferrira4041@gmail.com</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>5591985549309</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>canaã - regulares | agronomia 08/2026</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Canaã</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>AGR - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>como é que eu consigo fazer esse jogo</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>netocarlos436@gmail.com</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>5594991210960</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>canaã - regulares | agronomia 08/2026</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Canaã</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>AGR - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Abel Gonçalves de Almeida</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>abelgoncalvesdealmeida@gmail.com</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>5594984275242</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>canaã - regulares | agronomia 08/2026</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Canaã</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>AGR - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Welis Santos da Silva</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>welissilva2020@gmail.com</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>5593991748866</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>canaã - regulares | agronomia 08/2026</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Canaã</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>AGR - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Edimilson Alves Pereira</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>edimilsonalvespereira416@gmail.com</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>5594991113616</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>canaã - regulares | agronomia 08/2026</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Canaã</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>AGR - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Eduarda</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>botelhoeduarda784@gmail.com</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>5594992737651</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>canaã - regulares | agronomia 08/2026</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Canaã</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>AGR - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Antonio Gomes Da Silva Gomes da Silva</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>matraquinham@gmail.com</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>5594984202729</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>canaã - regulares | agronomia 08/2026</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Canaã</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>AGR - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Jose Sidney Almeida Chaves Almeida</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>jos20chaves@gmail.com</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>5594988136142</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>canaã - regulares | agronomia 08/2026</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Canaã</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>AGR - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Waltoves Assis</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>waltoves.assis@hotmail.com</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>5594991694818</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>canaã - regulares | agronomia 08/2026</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Canaã</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>AGR - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Thauany</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>silvathauany639@gmail.com</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>94991947696</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
           <t>canaã - regulares | to 07/2026</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Canaã</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Canaã</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>TO - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Adeanny da Conceicao</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>mariaadeane87@gmail.com</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>5594992923076</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>canaã - regulares | to 07/2026</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Canaã</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>TO - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>David Azevedo</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>davidazeved123@gmail.com</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>5594992947948</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>canaã - regulares | to 07/2026</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Canaã</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
         <is>
           <t>TO - Formulário Meta</t>
         </is>

--- a/novos_leads.xlsx
+++ b/novos_leads.xlsx
@@ -451,17 +451,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Vanusa Fernandes</t>
+          <t>Christine Vianna</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>vanusafernandesgreg@gmail.com</t>
+          <t>christinevianna9@gmail.com</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>5531975612963</t>
+          <t>5531999612556</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -483,17 +483,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Camila Brandão</t>
+          <t>Fernanda Gonçalves</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>camila_kamilinha@live.com</t>
+          <t>ffg212016@gmail.com</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>5531988836718</t>
+          <t>5531997736482</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cláudia Caldeira</t>
+          <t>Carla Da Mata</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>apaidacaldeira@hotmail.com</t>
+          <t>carladamata301@gmail.com</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>5531995566093</t>
+          <t>5531973134872</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -547,17 +547,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Delfina mariaFerreira de sena</t>
+          <t>Eveline Barbosa</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>delfinamariaferreirasenad@gmail.com</t>
+          <t>evelineebarbosa@hotmail.com</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5531982698672</t>
+          <t>31988812814</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -579,17 +579,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Luciana Aparecida</t>
+          <t>Elaine Cristina Oliveira</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>lucianasouza04100@gmail.com</t>
+          <t>ecoliveira2013@gmail.com</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>553185012972</t>
+          <t>5531980226071</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -611,17 +611,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Adilson Sousa</t>
+          <t>Gabriel Felipe</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>adilsonvitorp@hotmail.com</t>
+          <t>cirlenesantos928@gmail.com</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>5533988063657</t>
+          <t>553181027751</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -643,17 +643,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Fatima Alves</t>
+          <t>Aline Morais</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>famuscafnc10@hotmail.com</t>
+          <t>enilacms@gmail.com</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5531993287789</t>
+          <t>5531985991997</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -675,17 +675,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Marta Aparecida Prado Ribeiro</t>
+          <t>Sheilla Martins</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>martaappribeiro@gmail.com.br</t>
+          <t>sheilawizardguanhaes@gmail.com</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>553198229315</t>
+          <t>5533988442563</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -707,49 +707,49 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sandra Regina Antiorio</t>
+          <t>Kelly Souza</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>sanluc@uol.com.br</t>
+          <t>kellysouza1607@yahoo.com.br</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>5511981467299</t>
+          <t>5531995315309</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>lorena - medicina - transf.internacional 07/2026</t>
+          <t>itabirito - regulares | to 07/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Medicina Lorena</t>
+          <t>Itabirito</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Medicina - Formulário Meta</t>
+          <t>TO - Formulário Meta</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Maria Gabriela Boher</t>
+          <t>Gabriella Schumacher</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>marigaboher@gmail.com</t>
+          <t>gabisouto5@gmail.com</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5524999679167</t>
+          <t>595993294835</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -771,17 +771,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Marcella Assis</t>
+          <t>Jilse Macedo</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>marcellaassis003@gmail.com</t>
+          <t>jilmacedo123@gmail.com</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>5562994058338</t>
+          <t>22996222605</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -803,17 +803,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Vinicius Teotônio Gusmão</t>
+          <t>Cleber Lomassi</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>viniciusteo@hotmail.com</t>
+          <t>cleberlomassi@gmail.com</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>5533991508585</t>
+          <t>5517981565111</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -835,17 +835,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Diana de carvalho queiroz</t>
+          <t>Gustavo Souza</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>dianaqueiroz.contato@gmail.com</t>
+          <t>gustavotaxa@live.com</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>5585992447410</t>
+          <t>5531971223960</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -867,17 +867,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Roxania Castro</t>
+          <t>Pablo Souza</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>rox-castro@hotmail.com</t>
+          <t>eng.pablosouza@gmail.com</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>5592994035951</t>
+          <t>21991044312</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -899,49 +899,49 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Verônica Reis</t>
+          <t>Milca Oliveira</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>reisveronica048@gmail.com</t>
+          <t>milcagra82@gmail.com</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>5512992495613</t>
+          <t>5567992459131</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>lorena - regulares | to 07/2026</t>
+          <t>lorena - medicina - transf.internacional 07/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lorena</t>
+          <t>Medicina Lorena</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>TO - Formulário Meta</t>
+          <t>Medicina - Formulário Meta</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ketllin camilly dos santos oliveira</t>
+          <t>andreia  Aparecida de Jesus vargas</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ketllincamilly1058@gmail.com</t>
+          <t>andreiavargas286@gmail.com</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>5512992396305</t>
+          <t>5512981171738</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -963,17 +963,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Fabricia Oliveira</t>
+          <t>Sabrina Alves</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>fabriciamoreira947@gmail.com</t>
+          <t>sabrina2728alves@gmail.com</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>5512982747506</t>
+          <t>5512997513618</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -995,182 +995,182 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Regiane Mendes</t>
+          <t>André Nascimento</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>regiane3538@hotmail.com</t>
+          <t>andre.n10@hotmail.com</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>5512992609186</t>
+          <t>5594991470426</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>lorena - regulares | to 07/2026</t>
+          <t>canaã - regulares | arquitetura  08/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lorena</t>
+          <t>Canaã</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>TO - Formulário Meta</t>
+          <t>ARQ - Formulário Meta</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Mariana Souza</t>
+          <t>Levir Gonçalves</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>marianacarolinepradosilva516@gmail.com</t>
+          <t>amandadossantosgoncalves20@gmail.com</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>5512991306703</t>
+          <t>5594999533433</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>lorena - regulares | to 07/2026</t>
+          <t>canaã - regulares | arquitetura  08/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lorena</t>
+          <t>Canaã</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>TO - Formulário Meta</t>
+          <t>ARQ - Formulário Meta</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Juliana Campos da Silva</t>
+          <t>Nei Fialho Brito</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>jucampos.daniel@gmail.com</t>
+          <t>fialhobriton@gmail.com</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>5535992089097</t>
+          <t>5594991548966</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>lorena - regulares | to 07/2026</t>
+          <t>canaã - regulares | arquitetura  08/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lorena</t>
+          <t>Canaã</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>TO - Formulário Meta</t>
+          <t>ARQ - Formulário Meta</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Débora Martins</t>
+          <t>Alenilsom Oliveira</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>dm9742557@gmail.com</t>
+          <t>alenilsomoliveira805@gmail.com</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>5512987033258</t>
+          <t>5591981136702</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>lorena - regulares | to 07/2026</t>
+          <t>canaã - regulares | agronomia 08/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lorena</t>
+          <t>Canaã</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>TO - Formulário Meta</t>
+          <t>AGR - Formulário Meta</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Gloria Paula</t>
+          <t>Clenilson Silva melonio</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>gloriapaula971@gmail.com</t>
+          <t>Clenilsonmelonio34@gmail.com</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>5512996351169</t>
+          <t>94992226878</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>lorena - regulares | to 07/2026</t>
+          <t>canaã - regulares | agronomia 08/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lorena</t>
+          <t>Canaã</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>TO - Formulário Meta</t>
+          <t>AGR - Formulário Meta</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Mauro Santos Silva</t>
+          <t>Mailson Araújo de Souza</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>maurosantossilva2999@gmail.com</t>
+          <t>bidogomailsonaraujodesouza@gmail.com</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>5594984443493</t>
+          <t>556696872662</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>canaã - regulares | arquitetura  08/2026</t>
+          <t>canaã - regulares | agronomia 08/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1180,29 +1180,29 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ARQ - Formulário Meta</t>
+          <t>AGR - Formulário Meta</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rose Lopes</t>
+          <t>Rosana da Silva  Bomfim</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>roselia.martins19@gmail.com</t>
+          <t>rosanabonfim571@gmail.com</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>5594991563485</t>
+          <t>5594981241566</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>canaã - regulares | arquitetura  08/2026</t>
+          <t>canaã - regulares | agronomia 08/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1212,24 +1212,24 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ARQ - Formulário Meta</t>
+          <t>AGR - Formulário Meta</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Pedro Mendes Neto</t>
+          <t>Enir Gonçalves</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>mendesnetopedro@aol.com</t>
+          <t>enirgoncalves51@gmail.com</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>5594984190720</t>
+          <t>5594991166304</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1251,17 +1251,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Edilson Venâncio</t>
+          <t>Cicero Sampaio</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>edilsovenancio150@gmail.com</t>
+          <t>cicerovieirasampaio62@gmail.com</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>5594992206811</t>
+          <t>5594992381896</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Elionora Ferreira de Sa</t>
+          <t>Macos Dasilvacrus</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>elionoraferreira8@gmail.com</t>
+          <t>macosdasilvacrus@gmail.com</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>5594991499810</t>
+          <t>5594991405025</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1315,17 +1315,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sara Rocha</t>
+          <t>Aline Sousa</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>rochasara80@gmail.com</t>
+          <t>liviasousafonseca@gmail.com</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>5594988023795</t>
+          <t>5563974006603</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1347,17 +1347,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Lina D M Souza</t>
+          <t>Junior Do Trecho</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Lina954@outlook.com</t>
+          <t>junioreisreis492@gmail.com</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>94914249737</t>
+          <t>5594991936146</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1379,17 +1379,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Rita Ferreira De Sousa</t>
+          <t>Anna Macieira</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ritaferrira4041@gmail.com</t>
+          <t>anasilvamacieira17@icloud.com</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>5591985549309</t>
+          <t>5594984399318</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1411,17 +1411,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>como é que eu consigo fazer esse jogo</t>
+          <t>Leandro Guedes</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>netocarlos436@gmail.com</t>
+          <t>guedesdimem43@gmail.com</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>5594991210960</t>
+          <t>5594991912086</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1443,22 +1443,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Abel Gonçalves de Almeida</t>
+          <t>Mariana</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>abelgoncalvesdealmeida@gmail.com</t>
+          <t>mariannamaciell532@gmail.com</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>5594984275242</t>
+          <t>5594984075261</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>canaã - regulares | agronomia 08/2026</t>
+          <t>canaã - regulares | to 07/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1468,29 +1468,29 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>AGR - Formulário Meta</t>
+          <t>TO - Formulário Meta</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Welis Santos da Silva</t>
+          <t>Eliane Jayme</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>welissilva2020@gmail.com</t>
+          <t>jaymeeliane@gmail.com</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>5593991748866</t>
+          <t>5594992845149</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>canaã - regulares | agronomia 08/2026</t>
+          <t>canaã - regulares | to 07/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1500,29 +1500,29 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>AGR - Formulário Meta</t>
+          <t>TO - Formulário Meta</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Edimilson Alves Pereira</t>
+          <t>Erika Cristina Sousa</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>edimilsonalvespereira416@gmail.com</t>
+          <t>erikaabreu751@gmail.com</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>5594991113616</t>
+          <t>5594991938834</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>canaã - regulares | agronomia 08/2026</t>
+          <t>canaã - regulares | to 07/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1532,29 +1532,29 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>AGR - Formulário Meta</t>
+          <t>TO - Formulário Meta</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Eduarda</t>
+          <t>Valdeniza Lima</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>botelhoeduarda784@gmail.com</t>
+          <t>valdenizadamatalima@gmail.com</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>5594992737651</t>
+          <t>5594992526242</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>canaã - regulares | agronomia 08/2026</t>
+          <t>canaã - regulares | to 07/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1564,29 +1564,29 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>AGR - Formulário Meta</t>
+          <t>TO - Formulário Meta</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Antonio Gomes Da Silva Gomes da Silva</t>
+          <t>Raylma Sousa</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>matraquinham@gmail.com</t>
+          <t>raylmasousa01@gmail.com</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>5594984202729</t>
+          <t>5594984084913</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>canaã - regulares | agronomia 08/2026</t>
+          <t>canaã - regulares | to 07/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1596,29 +1596,29 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>AGR - Formulário Meta</t>
+          <t>TO - Formulário Meta</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Jose Sidney Almeida Chaves Almeida</t>
+          <t>Liana do nascimento Louzeiro de Oliveira</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>jos20chaves@gmail.com</t>
+          <t>missao2789@gmail.com</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>5594988136142</t>
+          <t>5598984034896</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>canaã - regulares | agronomia 08/2026</t>
+          <t>canaã - regulares | to 07/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1628,29 +1628,29 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>AGR - Formulário Meta</t>
+          <t>TO - Formulário Meta</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Waltoves Assis</t>
+          <t>Sandrely Alves</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>waltoves.assis@hotmail.com</t>
+          <t>sandrelyalves@hotmail.com</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>5594991694818</t>
+          <t>5594984104969</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>canaã - regulares | agronomia 08/2026</t>
+          <t>canaã - regulares | to 07/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1660,24 +1660,24 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>AGR - Formulário Meta</t>
+          <t>TO - Formulário Meta</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Thauany</t>
+          <t>Francisca Ferreira de Lima</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>silvathauany639@gmail.com</t>
+          <t>francylima05@gmail.com</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>94991947696</t>
+          <t>5594988094742</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1699,17 +1699,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Adeanny da Conceicao</t>
+          <t>Isabel Piris</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>mariaadeane87@gmail.com</t>
+          <t>izabelpires135@gmail.com</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>5594992923076</t>
+          <t>5594992170932</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1731,17 +1731,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>David Azevedo</t>
+          <t>Laís Moraes</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>davidazeved123@gmail.com</t>
+          <t>laismoraesdossantos914@gmail.com</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>5594992947948</t>
+          <t>5594992820858</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">

--- a/novos_leads.xlsx
+++ b/novos_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,17 +451,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Christine Vianna</t>
+          <t>Evaldete Henrique de Souza Nogueira</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>christinevianna9@gmail.com</t>
+          <t>evaldetehenrique@gmail.com</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>5531999612556</t>
+          <t>5531973012460</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -483,17 +483,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Fernanda Gonçalves</t>
+          <t>jussara da costa crispim</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ffg212016@gmail.com</t>
+          <t>jussaradacostacrispim@gmail.com</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>5531997736482</t>
+          <t>5531982341919</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Carla Da Mata</t>
+          <t>Ana Maria Freitas</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>carladamata301@gmail.com</t>
+          <t>anamariafreitas37@gmail.com</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>5531973134872</t>
+          <t>5515982676437</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -547,17 +547,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Eveline Barbosa</t>
+          <t>Arethuza Antunes dos Santos</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>evelineebarbosa@hotmail.com</t>
+          <t>arearts@yahoo.com.br</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>31988812814</t>
+          <t>5531999142128</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -579,177 +579,157 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Elaine Cristina Oliveira</t>
+          <t>Saskia Rafaela Fernandes</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ecoliveira2013@gmail.com</t>
+          <t>homeofficesaskia@gmail.com</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5531980226071</t>
+          <t>5512991701833</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>itabirito - regulares | to 07/2026</t>
+          <t>lorena - regulares | wpp 07/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Itabirito</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>TO - Formulário Meta</t>
-        </is>
-      </c>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Gabriel Felipe</t>
+          <t>𝔄𝔫𝔞 𝔍𝔲𝔩𝔦𝔞</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>cirlenesantos928@gmail.com</t>
+          <t>anasilvajulia0978@gmail.com</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>553181027751</t>
+          <t>5535991114415</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>itabirito - regulares | to 07/2026</t>
+          <t>lorena - regulares | wpp 07/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Itabirito</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>TO - Formulário Meta</t>
-        </is>
-      </c>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Aline Morais</t>
+          <t>Danilo Rodrigues</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>enilacms@gmail.com</t>
+          <t>rodriguesdro@gmail.com</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5531985991997</t>
+          <t>5512982793060</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>itabirito - regulares | to 07/2026</t>
+          <t>lorena - regulares | wpp 07/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Itabirito</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>TO - Formulário Meta</t>
-        </is>
-      </c>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sheilla Martins</t>
+          <t>Tatinha Vieira</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>sheilawizardguanhaes@gmail.com</t>
+          <t>mh0376430@gmail.com</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>5533988442563</t>
+          <t>5512982400147</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>itabirito - regulares | to 07/2026</t>
+          <t>lorena - regulares | wpp 07/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Itabirito</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>TO - Formulário Meta</t>
-        </is>
-      </c>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Kelly Souza</t>
+          <t>Claudia Da Silva</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>kellysouza1607@yahoo.com.br</t>
+          <t>claudiasilvaonline2023@gmail.com</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>5531995315309</t>
+          <t>5512996403315</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>itabirito - regulares | to 07/2026</t>
+          <t>lorena - regulares | wpp 07/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Itabirito</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>TO - Formulário Meta</t>
-        </is>
-      </c>
+          <t>Lorena</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Gabriella Schumacher</t>
+          <t>Lucas Ruan</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>gabisouto5@gmail.com</t>
+          <t>lucas.ruan.gatinho@hotmail.com</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>595993294835</t>
+          <t>5583987959160</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -771,17 +751,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Jilse Macedo</t>
+          <t>Sérgio Filho</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>jilmacedo123@gmail.com</t>
+          <t>montado.quilha.2w@icloud.com</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>22996222605</t>
+          <t>556493084164</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -803,17 +783,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cleber Lomassi</t>
+          <t>Fernando  coture budal</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>cleberlomassi@gmail.com</t>
+          <t>prof.fernandobudal@gmail.com</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>5517981565111</t>
+          <t>5541984105898</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -835,17 +815,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Gustavo Souza</t>
+          <t>Adolfo Ojeda</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>gustavotaxa@live.com</t>
+          <t>tigrinho28@gmail.com</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>5531971223960</t>
+          <t>595982283564</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -867,17 +847,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Pablo Souza</t>
+          <t>eliene</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>eng.pablosouza@gmail.com</t>
+          <t>eeliennysiusa@gmail.com</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>21991044312</t>
+          <t>5585981153402</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -899,17 +879,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Milca Oliveira</t>
+          <t>SBPC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>milcagra82@gmail.com</t>
+          <t>medicorogerioh@gmail.com</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>5567992459131</t>
+          <t>5549999820572</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -931,145 +911,145 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>andreia  Aparecida de Jesus vargas</t>
+          <t>Felix Winkel</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>andreiavargas286@gmail.com</t>
+          <t>felixmw@hotmail.com</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>5512981171738</t>
+          <t>447412624445</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>lorena - regulares | to 07/2026</t>
+          <t>lorena - medicina - transf.internacional 07/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lorena</t>
+          <t>Medicina Lorena</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>TO - Formulário Meta</t>
+          <t>Medicina - Formulário Meta</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sabrina Alves</t>
+          <t>Gustavo Felipe Vilela</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>sabrina2728alves@gmail.com</t>
+          <t>gustavofgomespvilela@gmail.com</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>5512997513618</t>
+          <t>595992075113</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>lorena - regulares | to 07/2026</t>
+          <t>lorena - medicina - transf.internacional 07/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lorena</t>
+          <t>Medicina Lorena</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>TO - Formulário Meta</t>
+          <t>Medicina - Formulário Meta</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>André Nascimento</t>
+          <t>Rejane Baldez</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>andre.n10@hotmail.com</t>
+          <t>rejanebaldez@gmail.com</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>5594991470426</t>
+          <t>5551993263333</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>canaã - regulares | arquitetura  08/2026</t>
+          <t>lorena - medicina - transf.internacional 07/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Canaã</t>
+          <t>Medicina Lorena</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ARQ - Formulário Meta</t>
+          <t>Medicina - Formulário Meta</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Levir Gonçalves</t>
+          <t>JonasFBV</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>amandadossantosgoncalves20@gmail.com</t>
+          <t>balod@hotmail.com</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>5594999533433</t>
+          <t>5531991439458</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>canaã - regulares | arquitetura  08/2026</t>
+          <t>lorena - medicina - transf.internacional 07/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Canaã</t>
+          <t>Medicina Lorena</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ARQ - Formulário Meta</t>
+          <t>Medicina - Formulário Meta</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Nei Fialho Brito</t>
+          <t>𝕴𝖘𝖗𝖆𝖊𝖑</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>fialhobriton@gmail.com</t>
+          <t>israelconceicaosousa45@gmail.com</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>5594991548966</t>
+          <t>5594991641799</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1091,22 +1071,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Alenilsom Oliveira</t>
+          <t>Roberto Leite Da Silva Leite da Silva</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>alenilsomoliveira805@gmail.com</t>
+          <t>alandasilva20252023@gmail.com</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>5591981136702</t>
+          <t>5594992711216</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>canaã - regulares | agronomia 08/2026</t>
+          <t>canaã - regulares | arquitetura  08/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1116,24 +1096,24 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>AGR - Formulário Meta</t>
+          <t>ARQ - Formulário Meta</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Clenilson Silva melonio</t>
+          <t>Elainy Mestre</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Clenilsonmelonio34@gmail.com</t>
+          <t>elaineteixeira@gmail.com</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>94992226878</t>
+          <t>5594991236060</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1155,17 +1135,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Mailson Araújo de Souza</t>
+          <t>Joao Carlos De Oliveira</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>bidogomailsonaraujodesouza@gmail.com</t>
+          <t>joaocarlosd365@gmail.com</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>556696872662</t>
+          <t>5593991078705</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1187,17 +1167,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rosana da Silva  Bomfim</t>
+          <t>Melcleye de Carvalho Cambraia</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>rosanabonfim571@gmail.com</t>
+          <t>cambraiamel@gmail.com</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>5594981241566</t>
+          <t>5591985926095</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1219,17 +1199,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Enir Gonçalves</t>
+          <t>Natanael P D Silva</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>enirgoncalves51@gmail.com</t>
+          <t>natanaelpdsilva62@gmail.com</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>5594991166304</t>
+          <t>5594992181337</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1251,17 +1231,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Cicero Sampaio</t>
+          <t>Sidiney Ferraz Ferraz</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>cicerovieirasampaio62@gmail.com</t>
+          <t>sidineyferraz5@gmail.com</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>5594992381896</t>
+          <t>5594991506866</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1283,17 +1263,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Macos Dasilvacrus</t>
+          <t>Vitoria Alexia</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>macosdasilvacrus@gmail.com</t>
+          <t>vitoriacarvalho0103@gmail.com</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>5594991405025</t>
+          <t>5594992024824</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1315,17 +1295,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Aline Sousa</t>
+          <t>@marwoou</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>liviasousafonseca@gmail.com</t>
+          <t>marquesravel54@gmail.com</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>5563974006603</t>
+          <t>5594984440984</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1347,17 +1327,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Junior Do Trecho</t>
+          <t>angelica ⼡ oliveira </t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>junioreisreis492@gmail.com</t>
+          <t>gatomago2022@proton.me</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>5594991936146</t>
+          <t>5594991855688</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1379,17 +1359,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Anna Macieira</t>
+          <t>Edinaldo PingoletaEdinaldo nunes dos Santos</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>anasilvamacieira17@icloud.com</t>
+          <t>gomesraimundogomesdeoliveira3@gmail.com</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>5594984399318</t>
+          <t>5594984453943</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1411,17 +1391,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Leandro Guedes</t>
+          <t>Marcos Oliveira</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>guedesdimem43@gmail.com</t>
+          <t>marcosoliveira552412@hotmail.com</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>5594991912086</t>
+          <t>5599991406310</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1443,22 +1423,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Mariana</t>
+          <t>Francisco Souza</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>mariannamaciell532@gmail.com</t>
+          <t>chicobarros849@gmail.com</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>5594984075261</t>
+          <t>5594991475605</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>canaã - regulares | to 07/2026</t>
+          <t>canaã - regulares | agronomia 08/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1468,29 +1448,29 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>TO - Formulário Meta</t>
+          <t>AGR - Formulário Meta</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Eliane Jayme</t>
+          <t>Edivaldo Sena</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>jaymeeliane@gmail.com</t>
+          <t>secreta.03.03@gmail.com</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>5594992845149</t>
+          <t>5591981193647</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>canaã - regulares | to 07/2026</t>
+          <t>canaã - regulares | agronomia 08/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1500,29 +1480,29 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>TO - Formulário Meta</t>
+          <t>AGR - Formulário Meta</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Erika Cristina Sousa</t>
+          <t>Leandro de Sousa</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>erikaabreu751@gmail.com</t>
+          <t>lsousa77727@gmail.com</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>5594991938834</t>
+          <t>5594991658244</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>canaã - regulares | to 07/2026</t>
+          <t>canaã - regulares | agronomia 08/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1532,29 +1512,29 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>TO - Formulário Meta</t>
+          <t>AGR - Formulário Meta</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Valdeniza Lima</t>
+          <t>Noé Rocha Braga</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>valdenizadamatalima@gmail.com</t>
+          <t>rochabraga.vendas@gmail.com</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>5594992526242</t>
+          <t>5594984215391</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>canaã - regulares | to 07/2026</t>
+          <t>canaã - regulares | agronomia 08/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1564,29 +1544,29 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>TO - Formulário Meta</t>
+          <t>AGR - Formulário Meta</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Raylma Sousa</t>
+          <t>Maria Bomfim Borges da Silva</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>raylmasousa01@gmail.com</t>
+          <t>mariabonfimborgesdasilva@gmail.com</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>5594984084913</t>
+          <t>5594991259525</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>canaã - regulares | to 07/2026</t>
+          <t>canaã - regulares | agronomia 08/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1596,29 +1576,29 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>TO - Formulário Meta</t>
+          <t>AGR - Formulário Meta</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Liana do nascimento Louzeiro de Oliveira</t>
+          <t>Rnny</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>missao2789@gmail.com</t>
+          <t>ronycardoso1122@gmail.com</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>5598984034896</t>
+          <t>5594993009610</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>canaã - regulares | to 07/2026</t>
+          <t>canaã - regulares | agronomia 08/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1628,29 +1608,29 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>TO - Formulário Meta</t>
+          <t>AGR - Formulário Meta</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sandrely Alves</t>
+          <t>Hernandes</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>sandrelyalves@hotmail.com</t>
+          <t>hernandes.eu.br@gmail.com</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>5594984104969</t>
+          <t>5594984120126</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>canaã - regulares | to 07/2026</t>
+          <t>canaã - regulares | agronomia 08/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1660,29 +1640,29 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>TO - Formulário Meta</t>
+          <t>AGR - Formulário Meta</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Francisca Ferreira de Lima</t>
+          <t>Expedita Brandão De Sousa</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>francylima05@gmail.com</t>
+          <t>expeditarrodrigues56@gmail.com</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>5594988094742</t>
+          <t>5594984255461</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>canaã - regulares | to 07/2026</t>
+          <t>canaã - regulares | agronomia 08/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1692,29 +1672,29 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>TO - Formulário Meta</t>
+          <t>AGR - Formulário Meta</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Isabel Piris</t>
+          <t>Diones de jesus Oliveira</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>izabelpires135@gmail.com</t>
+          <t>dionesdejesus678@gmail.com</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>5594992170932</t>
+          <t>559491978207</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>canaã - regulares | to 07/2026</t>
+          <t>canaã - regulares | agronomia 08/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1724,37 +1704,293 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>TO - Formulário Meta</t>
+          <t>AGR - Formulário Meta</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Laís Moraes</t>
+          <t>Claudean Aguiar</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>laismoraesdossantos914@gmail.com</t>
+          <t>claudeanaguiar488@gmail.com</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>5594992820858</t>
+          <t>5594991851341</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
+          <t>canaã - regulares | agronomia 08/2026</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Canaã</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>AGR - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Wellington Da Silva</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>wellingtonlopesagro2016@gmail.com</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>5593988171934</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
           <t>canaã - regulares | to 07/2026</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Canaã</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Canaã</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>TO - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Ana Machado</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>hanna.312@hotmail.com</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>5594992296182</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>canaã - regulares | to 07/2026</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Canaã</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>TO - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Rayssa Monteiro</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>rayssarafaelle04@iCloud.com</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>5594981095506</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>canaã - regulares | to 07/2026</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Canaã</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>TO - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Edinice Da Silva Lima</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>edinicedasilvalima@gmail.com</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>5594991409803</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>canaã - regulares | to 07/2026</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Canaã</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>TO - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Cleiane Fernandes</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>cleianefernandes36@gmail.com</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>5598985448442</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>canaã - regulares | to 07/2026</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Canaã</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>TO - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Damires Silva </t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>silvdamires94@gmail.com</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>5594991902908</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>canaã - regulares | to 07/2026</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Canaã</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>TO - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Noemi Da Silva Batista</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>miryandasilv09@gmail.com</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>5594991697357</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>canaã - regulares | to 07/2026</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Canaã</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>TO - Formulário Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>F.R</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>ruanaflavia16@gmail.com</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>5594992074210</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>canaã - regulares | to 07/2026</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Canaã</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
         <is>
           <t>TO - Formulário Meta</t>
         </is>
